--- a/output/pdf_financials_xlsx/BLM.xlsx
+++ b/output/pdf_financials_xlsx/BLM.xlsx
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007348</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.461618</v>
+        <v>-1.45427</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-3.110057</v>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.412958</v>
+        <v>-1.40561</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-3.018371</v>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-18.57801023990407</v>
+        <v>-18.48139645574147</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>-36.11400956819869</v>
@@ -2529,19 +2529,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.322578</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.317687</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.5607490000000001</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.027439</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.219372</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
@@ -2556,16 +2556,16 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.022117</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.243098</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>4.72742</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.911423</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>3.04</v>
@@ -2639,19 +2639,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.322578</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.317687</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.5607490000000001</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.027439</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.219372</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
@@ -2666,16 +2666,16 @@
         <v>0.1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.022117</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.243098</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>4.72742</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>4.911423</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>3.04</v>
@@ -3299,19 +3299,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.710638</v>
+        <v>0.38806</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.554414</v>
+        <v>0.236727</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.834181</v>
+        <v>0.273432</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.165812</v>
+        <v>0.138373</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.013188</v>
+        <v>0.793816</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>2.861391</v>
@@ -3326,16 +3326,16 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.218272</v>
+        <v>5.196155</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.489799</v>
+        <v>4.246701</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>10.964108</v>
+        <v>6.236688</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>10.357327</v>
+        <v>5.445904</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>8.147</v>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -17508,7 +17508,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -21510,7 +21510,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -36638,7 +36638,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -38736,7 +38736,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E319" s="5" t="n">
@@ -70910,7 +70910,7 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E655" s="5" t="n">
@@ -71010,7 +71010,7 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E656" s="5" t="n">

--- a/output/pdf_financials_xlsx/BLM.xlsx
+++ b/output/pdf_financials_xlsx/BLM.xlsx
@@ -2208,22 +2208,22 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.05997</v>
+        <v>0.096286</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.057346</v>
+        <v>0.088089</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.288571</v>
+        <v>0.763149</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.461296</v>
+        <v>1.255899</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.376574</v>
+        <v>0.810138</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.299956</v>
+        <v>0.474659</v>
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
@@ -2246,13 +2246,13 @@
         </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.021</v>
+        <v>0.08</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.024</v>
+        <v>0.103</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>1.677</v>
+        <v>1.862</v>
       </c>
     </row>
     <row r="29">
@@ -2273,22 +2273,22 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.195425</v>
+        <v>-1.159109</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.882866</v>
+        <v>-0.852123</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.067146</v>
+        <v>-1.592568</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-6.440828</v>
+        <v>-5.646225</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.392164</v>
+        <v>1.825728</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.888321</v>
+        <v>1.063024</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.964</v>
+        <v>1.023</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.295</v>
+        <v>0.374</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.192</v>
+        <v>0.377</v>
       </c>
     </row>
     <row r="30">
@@ -2338,22 +2338,22 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-38.69704961399254</v>
+        <v>-37.52146598994105</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-11.82174336522787</v>
+        <v>-11.41008875821254</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-6.552135690059151</v>
+        <v>-5.047888069660353</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-23.58519387374982</v>
+        <v>-20.675495647425</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>4.158344982496385</v>
+        <v>5.453385426000932</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.820640196840024</v>
+        <v>3.375365689436217</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -2376,13 +2376,13 @@
         </is>
       </c>
       <c r="O30" s="3" t="n">
-        <v>2.747691255273059</v>
+        <v>2.915859081062592</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.8467765084103565</v>
+        <v>1.073540386933808</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0.306787677361626</v>
+        <v>0.6023903873194427</v>
       </c>
     </row>
     <row r="31">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.04866</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.091686</v>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
@@ -6204,43 +6204,43 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.096286</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.088089</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.763149</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>1.255899</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.810138</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.474659</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.178358</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.10587</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.078541</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.075917</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>1.862</v>
       </c>
     </row>
     <row r="101">
@@ -39308,7 +39308,11 @@
           <t>Depreciation of property and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -39402,7 +39406,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -42680,7 +42684,11 @@
           <t>Depreciation of property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -42776,7 +42784,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -44580,7 +44588,11 @@
           <t>Depreciation of property, plant and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
@@ -46694,7 +46706,11 @@
           <t>Depreciation of property, plant and equipment (note 5) 99,280</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -46792,7 +46808,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -49908,7 +49924,11 @@
           <t>Depreciation of property, plant and equipment 5</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -50002,7 +50022,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -54468,7 +54488,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
@@ -54560,7 +54584,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -60404,7 +60428,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E546" s="5" t="n">
@@ -70528,7 +70552,7 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E651" s="5" t="n">

--- a/output/pdf_financials_xlsx/BLM.xlsx
+++ b/output/pdf_financials_xlsx/BLM.xlsx
@@ -2859,37 +2859,37 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.170131</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.133101</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.132517</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.132002</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.601302</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.144867</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.428922</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.330464</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.025258</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.002789</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.031938</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>0</v>
@@ -2914,37 +2914,37 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>1.927756</v>
+        <v>2.097887</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>2.377041</v>
+        <v>2.510142</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>1.185195</v>
+        <v>1.317712</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.763771</v>
+        <v>0.895773</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2.399921</v>
+        <v>3.001223</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>7.204156</v>
+        <v>7.349023</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>5.038457</v>
+        <v>5.467379</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>7.226548</v>
+        <v>7.557012</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4.547825</v>
+        <v>4.573083</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>5.307302</v>
+        <v>5.310091</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>3.839265</v>
+        <v>3.871203</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>4.717157</v>
@@ -3299,25 +3299,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.38806</v>
+        <v>0.217929</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.236727</v>
+        <v>0.103626</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.273432</v>
+        <v>0.140915</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.138373</v>
+        <v>0.006371</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.793816</v>
+        <v>0.192514</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.861391</v>
+        <v>2.716524</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.428234</v>
+        <v>1.999312</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.196155</v>
+        <v>5.193366</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.246701</v>
+        <v>4.214763</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>6.236688</v>
@@ -7122,34 +7122,34 @@
         <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.320016</v>
       </c>
       <c r="H116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.015012</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.01232</v>
       </c>
       <c r="K116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.0288</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.02221</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.037772</v>
       </c>
       <c r="O116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-0.435</v>
       </c>
       <c r="Q116" s="3" t="n">
         <v>0</v>
@@ -7302,15 +7302,11 @@
       <c r="H119" s="3" t="n">
         <v>-0.861442</v>
       </c>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="3" t="n">
+        <v>0.213601</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>0.697966</v>
       </c>
       <c r="K119" s="3" t="n">
         <v>0.067777</v>
@@ -7904,15 +7900,11 @@
       <c r="F129" s="3" t="n">
         <v>0.905775</v>
       </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G129" s="3" t="n">
+        <v>-0.169503</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>0.414068</v>
       </c>
       <c r="I129" s="3" t="n">
         <v>-0.291077</v>
@@ -8270,25 +8262,17 @@
       <c r="F135" s="3" t="n">
         <v>-0.713664</v>
       </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G135" s="3" t="n">
+        <v>-0.633213</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>0.6932</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>0.126603</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>-0.034015</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-1.093264</v>
@@ -39122,7 +39106,11 @@
           <t>Deferred income tax expense (note 17)</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -42024,7 +42012,11 @@
           <t>Acquisition of intangible asset (note 8)</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -42496,7 +42488,11 @@
           <t>Deferred tax expense (note 13)</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -43548,7 +43544,11 @@
           <t>Acquisition of intangible asset (note 7)</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -50872,7 +50872,11 @@
           <t>Net cash generated by (used in) operating activities</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
           <t>-</t>
@@ -51156,7 +51160,11 @@
           <t>Acquisition of intangible assets 6</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
@@ -53344,7 +53352,11 @@
           <t>Net cash generated by operating activities</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -55248,7 +55260,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -55728,7 +55744,11 @@
           <t>Net cash generated by (used in) operating activities</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E497" t="inlineStr">
         <is>
           <t>-</t>
@@ -55920,7 +55940,11 @@
           <t>Acquisition of intangible assets 7</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
           <t>-</t>
@@ -61858,7 +61882,11 @@
           <t>Issuance of shares on private placement</t>
         </is>
       </c>
-      <c r="D561" t="inlineStr"/>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E561" s="5" t="n">
         <v>0.45523</v>
       </c>
